--- a/jainam/Ayush Keys.xlsx
+++ b/jainam/Ayush Keys.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Rohan_Do_Not_Delete\Ayussh\godseye\jainam\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCA4A33-B6A6-4642-A19A-7FED66A330E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3810" yWindow="3810" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19890" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -61,118 +68,449 @@
     <t>ROC</t>
   </si>
   <si>
+    <t>Sumit</t>
+  </si>
+  <si>
+    <t>6DIT02</t>
+  </si>
+  <si>
+    <t>Ram@234</t>
+  </si>
+  <si>
+    <t>GIMLXIZYGP4OJQNC</t>
+  </si>
+  <si>
+    <t>a1SrPXFukK</t>
+  </si>
+  <si>
+    <t>Algo</t>
+  </si>
+  <si>
+    <t>MyREC8ji3xuy8XHn6v4VRCw0CHgqHcJQS8uBiqbuOPqKI3rgBHnP7YkhWXtoTi1b</t>
+  </si>
+  <si>
+    <t>http://127.0.0.1:5000/</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
+    <t>IFTIKHAR_JAINAM</t>
+  </si>
+  <si>
+    <t>ITC2851</t>
+  </si>
+  <si>
+    <t>Am@234</t>
+  </si>
+  <si>
+    <t>0ba5b6786d645e2c4ec814</t>
+  </si>
+  <si>
+    <t>Goddseye</t>
+  </si>
+  <si>
+    <t>Lvve826@yi</t>
+  </si>
+  <si>
     <t>http://127.0.0.1:5000</t>
-  </si>
-  <si>
-    <t>Goddseye</t>
-  </si>
-  <si>
-    <t>IFTIKHAR_JAINAM</t>
-  </si>
-  <si>
-    <t>ITC2851</t>
-  </si>
-  <si>
-    <t>Am@234</t>
-  </si>
-  <si>
-    <t>0ba5b6786d645e2c4ec814</t>
-  </si>
-  <si>
-    <t>Lvve826@yi</t>
-  </si>
-  <si>
-    <t>RACHITA</t>
-  </si>
-  <si>
-    <t>SN11111</t>
-  </si>
-  <si>
-    <t>Ram@345</t>
-  </si>
-  <si>
-    <t>SDZ35EEUQZIA45AQ</t>
-  </si>
-  <si>
-    <t>lJzgmU511p</t>
-  </si>
-  <si>
-    <t>Goddseye Algo</t>
-  </si>
-  <si>
-    <t>PygdDKGx000Z9xEl5pggs78e6rw6CLrBXS2sem3Tx2t8CzTLFXhOiyQCS2kDErGG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF121212"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3C3C3C"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -195,35 +533,316 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -508,31 +1127,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr defaultColWidth="8.85714285714286" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="71.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.4285714285714" customWidth="1"/>
+    <col min="2" max="2" width="10.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,119 +1181,132 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="E2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="6">
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" t="s">
-        <v>13</v>
       </c>
       <c r="M3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:3">
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="2"/>
+    <row r="6" spans="3:3">
+      <c r="C6" s="2"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C8" s="2"/>
+    <row r="13" spans="3:3">
+      <c r="C13" s="2"/>
     </row>
-    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C9" s="2"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3"/>
+    <row r="14" spans="3:3">
+      <c r="C14" s="2"/>
     </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="5"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+    <row r="16" spans="3:3">
+      <c r="C16" s="2"/>
     </row>
-    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F12" s="3"/>
+    <row r="17" spans="3:3">
+      <c r="C17" s="2"/>
     </row>
-    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C13" s="2"/>
-      <c r="F13" s="3"/>
+    <row r="18" spans="3:7">
+      <c r="C18" s="2"/>
+      <c r="D18"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C14" s="2"/>
-      <c r="F14" s="3"/>
+    <row r="19" spans="2:7">
+      <c r="B19" s="5"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="6"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="6:6">
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="3:6">
+      <c r="C22" s="2"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="mailto:Am@234" xr:uid="{33BC352A-7C81-4B4E-879D-7EAB13C3F5D8}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{A1A336C6-B8EB-46D9-AF39-6CA164C87317}"/>
+    <hyperlink ref="C2" r:id="rId1" display="Ram@234"/>
+    <hyperlink ref="C3" r:id="rId2" display="Am@234"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/jainam/Ayush Keys.xlsx
+++ b/jainam/Ayush Keys.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -88,6 +88,66 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
+    <t xml:space="preserve">RACHITA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SN11111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ram@345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDZ35EEUQZIA45AQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lJzgmU511p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddseye Algo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PygdDKGx000Z9xEl5pggs78e6rw6CLrBXS2sem3Tx2t8CzTLFXhOiyQCS2kDErGG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://127.0.0.1:5000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GROWTH </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6DIT999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ram@456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB44BFZNH4MDIZR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Igitb89wV3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tF3D4kGFufUBqaTZ0xkxQ5sCMpYxXPKskzlXn5prv4JNx4GjEUIPdIO92VlmirC9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIJAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6DIT2006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3VQML3QBGZ55E3DJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JalbRXNaQH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goddseye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0i9ytEGEMjH5ua74JsZW6NOtRp4pwkjd5y8VlaOVtH0ZWnBoFORXBubV6Ig2Bv4g</t>
+  </si>
+  <si>
     <t xml:space="preserve">IFTIKHAR_JAINAM</t>
   </si>
   <si>
@@ -100,67 +160,49 @@
     <t xml:space="preserve">0ba5b6786d645e2c4ec814</t>
   </si>
   <si>
-    <t xml:space="preserve">Goddseye</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lvve826@yi</t>
   </si>
   <si>
-    <t xml:space="preserve">http://127.0.0.1:5000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RACHITA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SN11111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ram@345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDZ35EEUQZIA45AQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lJzgmU511p</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Goddseye Algo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PygdDKGx000Z9xEl5pggs78e6rw6CLrBXS2sem3Tx2t8CzTLFXhOiyQCS2kDErGG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GROWTH </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6DIT999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ram@456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB44BFZNH4MDIZR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Igitb89wV3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tF3D4kGFufUBqaTZ0xkxQ5sCMpYxXPKskzlXn5prv4JNx4GjEUIPdIO92VlmirC9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIJAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6DIT2006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3VQML3QBGZ55E3DJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JalbRXNaQH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0i9ytEGEMjH5ua74JsZW6NOtRp4pwkjd5y8VlaOVtH0ZWnBoFORXBubV6Ig2Bv4g</t>
+    <t xml:space="preserve">CLEAN_JAINAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITC2275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5b22950ea39e7fc9dd8340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foue023#nL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANAM_JAINAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITC2317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ram456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMNYLAIAZ3SFWUPG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1218698a0386fcb01be136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rnfw568@g#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHUJA_JAINAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ITC2319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2a36a98b302bd034518495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hsik733#vS</t>
   </si>
 </sst>
 </file>
@@ -170,7 +212,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,13 +251,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u val="single"/>
       <sz val="11"/>
       <color theme="10"/>
@@ -240,6 +275,20 @@
     <font>
       <sz val="12"/>
       <color rgb="FF121212"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3C3C3C"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -318,12 +367,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -331,23 +384,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -355,11 +420,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -616,269 +685,376 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M1048576"/>
   <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="F3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="0" t="n">
+      <c r="G3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="0" t="s">
+      <c r="I6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="0" t="n">
+      <c r="J7" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="0" t="s">
+      <c r="I8" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M8" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="0" t="n">
+      <c r="G9" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="0" t="s">
+      <c r="I9" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M9" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="0" t="n">
-        <v>0</v>
-      </c>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="2"/>
+      <c r="C13" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="2"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="2"/>
+      <c r="C17" s="3"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="2"/>
-      <c r="E18" s="3"/>
+      <c r="B18" s="14"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-      <c r="G18" s="3"/>
+      <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="9"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
+      <c r="B19" s="15"/>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="10"/>
-      <c r="F20" s="3"/>
+      <c r="F20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="2"/>
-      <c r="F22" s="3"/>
-    </row>
+      <c r="C21" s="3"/>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="Ram@234"/>
-    <hyperlink ref="C3" r:id="rId2" display="Am@234"/>
-    <hyperlink ref="C4" r:id="rId3" display="Ram@345"/>
+    <hyperlink ref="C3" r:id="rId2" display="Ram@345"/>
+    <hyperlink ref="C6" r:id="rId3" display="Am@234"/>
+    <hyperlink ref="C7" r:id="rId4" display="Am@234"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/jainam/Ayush Keys.xlsx
+++ b/jainam/Ayush Keys.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="66">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -203,6 +203,21 @@
   </si>
   <si>
     <t xml:space="preserve">Hsik733#vS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LD_JAINAM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sm@123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">443d71f297e180cae88860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xjbo528#kK</t>
   </si>
 </sst>
 </file>
@@ -367,7 +382,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -404,19 +419,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -686,10 +697,20 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M1048576"/>
-  <sheetFormatPr defaultColWidth="8.859375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="25.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="84.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="7.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="5.19"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -915,31 +936,31 @@
       <c r="B7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J7" s="0" t="s">
+      <c r="J7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -947,34 +968,34 @@
       <c r="A8" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="0" t="n">
+      <c r="H8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="0" t="s">
+      <c r="I8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="J8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -994,22 +1015,57 @@
       <c r="E9" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="0" t="s">
+      <c r="J9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1028,17 +1084,17 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C17" s="3"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="13"/>
+      <c r="F17" s="12"/>
       <c r="G17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="14"/>
+      <c r="B18" s="13"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="15"/>
+      <c r="B19" s="14"/>
       <c r="F19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1055,6 +1111,7 @@
     <hyperlink ref="C3" r:id="rId2" display="Ram@345"/>
     <hyperlink ref="C6" r:id="rId3" display="Am@234"/>
     <hyperlink ref="C7" r:id="rId4" display="Am@234"/>
+    <hyperlink ref="C10" r:id="rId5" display="Sm@123"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
